--- a/agent_comparison.xlsx
+++ b/agent_comparison.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10609"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/denmacair/Downloads/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E101EB6B-BB7C-0240-8EFF-9E6887F43F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="660" windowWidth="27640" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
   <si>
     <t>Категория</t>
   </si>
@@ -46,68 +40,106 @@
     <t>Пациент жалуется на высокое давление и головные боли. Подозревает гипертонию.</t>
   </si>
   <si>
-    <t>Пациент сообщает о **высоком артериальном давлении** и **головных болях**, подозревая у себя **гипертонию**. Это состояние требует немедленной оценки для подтверждения диагноза и предотвращения осложнений, таких как сердечно-сосудистые заболевания.</t>
-  </si>
-  <si>
-    <t>1. **Диагностика и лечение артериальной гипертензии у взрослых**
-   - **Определение артериальной гипертензии (АГ):**
-     - Систолическое АД ≥ **140 мм рт. ст.** и/или диастолическое АД ≥ **90 мм рт. ст.**.
-   - **Рекомендации по фармакотерапии:**
-     - Препараты первой линии: **ингибиторы АПФ**, **блокаторы кальциевых каналов**, **диуретики**.
-   - **Целевые значения АД:**
-     - **&lt;130/80 мм рт. ст.** для пациентов с высоким сердечно-сосудистым риском.
-   - **Мониторинг:**
-     - Регулярное измерение АД, оценка факторов риска (курение, сахарный диабет, дислипидемия).
-   - **Источник:** [Клинические рекомендации Минздрава РФ](https://cr.minzdrav.gov.ru/clin-rec/hypertension)
-   - **Дата обновления:** 15.01.2023
-   - **Уровень доказательности:** **A** (высокий).</t>
+    <t>Пациент жалуется на **высокое давление** и **головные боли**, подозревает у себя гипертонию. Симптомы могут указывать на **артериальную гипертензию (АГ)**, особенно если головные боли носят упорный характер, локализуются в затылочной области и сопровождаются другими признаками (например, шумом в ушах, головокружением, слабостью). Однако для постановки диагноза требуется подтверждение повышенных значений артериального давления (АД) в нескольких измерениях и исключение вторичных форм гипертензии.
+### **Доказательная база**
+#### **1. Клинические рекомендации Минздрава России**
+По запросу **"гипертония"** найдено **5 релевантных клинических рекомендаций** в официальном реестре Минздрава. Наиболее подходящая для взрослого пациента с подозрением на АГ:
+- **[Артериальная гипертензия у взрослых](https://cr.minzdrav.gov.ru/view-cr/62_3)** (ID: `62_3`, дата публикации: 10.03.2024, МКБ-10: I10, I11, I12, I13, I15, I95.2).
+#### **2. Алгоритмы действий врача (извлечено из клинической рекомендации)**
+В документе представлены **алгоритмы ведения пациентов с АГ**, включая:
+- **Приложение Б1**: Тактика ведения пациентов с АГ.
+- **Приложение Б2**: Алгоритм стандартного лечения АГ I–II стадий (для большинства пациентов, включая тех, у кого есть поражение органов-мишеней, цереброваскулярные заболевания, сахарный диабет или заболевания периферических артерий).
+- **Приложение Б3–Б6**: Стратегии лекарственной терапии при сочетании АГ с:
+  - Хронической болезнью почек (ХБП).
+  - Ишемической болезнью сердца (ИБС).
+  - Фибрилляцией предсердий (ФП).
+  - Резистентной АГ.
+**Ключевые моменты из алгоритмов:**
+1. **Диагностика**:
+   - Подтверждение АГ требует **не менее 2–3 измерений АД** в разные дни (с интервалом не менее 1–2 недель).
+   - Целевое АД для большинства пациентов: **&lt;140/90 мм рт. ст.** (при хорошей переносимости — до 130/80 мм рт. ст.).
+   - Обязательные обследования:
+     - Общий анализ крови и мочи.
+     - Биохимический анализ крови (креатинин, калий, глюкоза, липидный профиль).
+     - ЭКГ.
+     - Эхокардиография (при подозрении на поражение сердца).
+     - УЗИ почек (при подозрении на вторичную гипертензию).
+2. **Лечение**:
+   - **Первая линия терапии**: тиазидные диуретики, ингибиторы АПФ (ИАПФ), блокаторы рецепторов ангиотензина II (БРА), антагонисты кальция (АК).
+   - **Комбинированная терапия**: рекомендуется при АГ II–III стадии или высоком сердечно-сосудистом риске.
+   - **Резистентная АГ**: требует исключения вторичных причин и назначения спиронолактона (с осторожностью при ХБП).
+3. **Тактика при головных болях**:
+   - Головные боли при АГ часто связаны с **повышением диастолического давления** (&gt;110 мм рт. ст.) или **гипертоническими кризами**.
+   - При стойких головных болях необходимо исключить **цереброваскулярные осложнения** (например, транзиторную ишемическую атаку или инсульт).
+**Ссылка на полный текст рекомендаций**:
+[Артериальная гипертензия у взрослых (ID: 62_3)](https://cr.minzdrav.gov.ru/view-cr/62_3).
+### **Советы оператору**
+На основе анализа медицинского графа знаний и клинических рекомендаций:
+1. **Первоочередные вопросы пациенту**:
+   - **"Как часто возникают головные боли и при каком уровне давления?"**
+     *Цель*: Уточнить связь между симптомами и АД. Головные боли при АГ обычно появляются при **АД &gt;160/100 мм рт. ст.** или в утренние часы.
+   - **"Есть ли другие симптомы: шум в ушах, мелькание мушек перед глазами, головокружение, слабость?"**
+     *Цель*: Выявить признаки поражения органов-мишеней (мозг, сердце, почки).
+   - **"Были ли эпизоды потери сознания, судорог или нарушения речи?"**
+     *Цель*: Исключить гипертонический криз или цереброваскулярные осложнения.
+   - **"Есть ли наследственная предрасположенность к гипертонии или сердечно-сосудистым заболеваниям?"**
+     *Цель*: Оценить риск развития АГ.
+   - **"Принимаете ли вы какие-либо лекарства (например, оральные контрацептивы, НПВС, кортикостероиды)?"**
+     *Цель*: Выявить возможные причины вторичной гипертензии.
+2. **Рекомендации по дальнейшим действиям**:
+   - **Срочно направить на измерение АД** (если не измерялось ранее) и **консультацию терапевта/кардиолога** для подтверждения диагноза.
+   - **Исключить вторичные причины гипертензии** (например, заболевания почек, эндокринные нарушения) при наличии:
+     - Стойкой АГ у молодых (&lt;30 лет) или пожилых (&gt;60 лет).
+     - Резистентной АГ (АД не снижается на фоне 3 препаратов).
+     - Внезапного ухудшения контроля АГ.
+   - **Объяснить пациенту важность амбулаторного наблюдения**:
+     - АГ часто протекает бессимптомно, но приводит к тяжелым осложнениям (инфаркт, инсульт, ХБП).
+     - Необходимо **вести дневник АД** (измерять 2 раза в день утром и вечером).
+   - **Предупредить о немедленном обращении за медицинской помощью** при:
+     - АД &gt;180/120 мм рт. ст.
+     - Появлении сильных головных болей, тошноты, рвоты, нарушения зрения.
+     - Боли в груди, одышке, онемении конечностей.
+3. **Образовательные материалы для пациента**:
+   - Объяснить, что **головные боли не всегда связаны с АГ**, но требуют обследования.
+   - Подчеркнуть роль **здорового образа жизни**: снижение соли, жиров, регулярная физическая активность, отказ от курения и алкоголя.
+**Важно**: Если у пациента **гипертонический криз** (АД &gt;180/120 мм рт. ст. + симптомы поражения органов-мишеней), **необходимо экстренное направление в стационар**.</t>
+  </si>
+  <si>
+    <t>Не найдено</t>
   </si>
   <si>
     <t>На основе анализа медицинского графа знаний и клинических рекомендаций:
-1. **Первоочередные действия:**
-   - **Подтвердить диагноз гипертонии:**
-     - Рекомендовать пациенту **неоднократное измерение АД** в домашних условиях (утром и вечером) в течение нескольких дней.
-     - Использовать **амбулаторный мониторинг АД (СМАД)** при возможности для исключения "гипертонии белого халата".
-   - **Исключить вторичные причины гипертонии:**
-     - Проверить наличие симптомов, указывающих на **феохромоцитому**, **первичный гиперальдостеронизм** или **заболевания почек**.
-2. **Тактика ведения:**
-   - **Немедленное направление к врачу:**
-     - Если АД ≥ **180/120 мм рт. ст.** или есть симптомы поражения органов-мишеней (головные боли, головокружение, нарушения зрения), **срочно направить к терапевту или кардиологу**.
-   - **Обследование:**
-     - **Общий анализ крови и мочи**, **биохимический анализ крови** (креатинин, калий, глюкоза, липидный профиль).
-     - **ЭКГ** для оценки гипертрофии левого желудочка.
-     - **Эхокардиография** при подозрении на сердечную недостаточность.
-3. **Образовательные рекомендации для пациента:**
-   - Объяснить важность **снижения потребления соли**, **умеренной физической активности**, **отказа от курения** и **ограничения алкоголя**.
-   - Назначить **диету DASH** (богатая калием, магнием, клетчаткой).
-4. **Мониторинг и наблюдение:**
-   - Если диагноз подтвержден, **назначить терапию** в соответствии с клиническими рекомендациями.
-   - **Контроль АД** каждые 1–3 месяца в зависимости от тяжести состояния.
-**Важно:** При наличии **острых симптомов** (например, сильной головной боли, тошноты, нарушений зрения) **рекомендовать пациенту вызвать скорую помощь** для исключения гипертонического криза.</t>
-  </si>
-  <si>
-    <t>Пациент сообщает о наличии **высокого артериального давления** и **головных болей**, что может указывать на **артериальную гипертензию (гипертоническую болезнь)**. Симптомы требуют уточнения диагноза, оценки степени тяжести и назначения соответствующего лечения.</t>
-  </si>
-  <si>
-    <t>Для анализа проблемы пациента используются следующие клинические рекомендации:
-1. **Артериальная гипертензия у взрослых**
-   - **Источник:** Российское кардиологическое общество (РКО)
-   - **Ссылка:** [Клинические рекомендации по артериальной гипертензии (2023)](https://cr.rosminzdrav.ru/recommend/2023/Arterialnaya_gipertenziya_u_vzroslyh)
-   - **Ключевые моменты:**
-     - Диагноз артериальной гипертензии устанавливается при уровне **АД ≥ 140/90 мм рт. ст.** на основании среднего значения не менее двух измерений в разные дни.
-     - Головная боль не является специфичным симптомом гипертензии, но может наблюдаться при значительном повышении АД.
-     - Рекомендуется проведение дополнительных исследований (ЭКГ, ЭхоКГ, анализы крови и мочи) для оценки органных поражений и риска осложнений.
-2. **Диагностика и лечение артериальной гипертензии**
-   - **Источник:** Министерство здравоохранения Российской Федерации
-   - **Ссылка:** [Всероссийское научное общество кардиологов (2020)](https://www.rosminzdrav.ru/docs/ministry/10092)
-   - **Ключевые моменты:**
-     - Первичная диагностика включает измерение АД, сбор анамнеза, физикальное обследование.
-     - Лечение начинается с модификации образа жизни (снижение массы тела, диета, физическая активность).
-     - Медикаментозная терапия назначается при неэффективности немедикаментозных методов или высоком риске осложнений.
-**Рекомендации пациенту:**
-- Пройти **амбулаторное или стационарное обследование** для подтверждения диагноза.
-- Измерять **артериальное давление** в динамике (желательно дома, в спокойной обстановке).
-- При подтверждении гипертензии следовать рекомендациям врача по лечению и профилактике осложнений.</t>
+1. **Первоочередные вопросы пациенту**:
+   - **"Как часто возникают головные боли и при каком уровне давления?"**
+     *Цель*: Уточнить связь между симптомами и АД. Головные боли при АГ обычно появляются при **АД &gt;160/100 мм рт. ст.** или в утренние часы.
+   - **"Есть ли другие симптомы: шум в ушах, мелькание мушек перед глазами, головокружение, слабость?"**
+     *Цель*: Выявить признаки поражения органов-мишеней (мозг, сердце, почки).
+   - **"Были ли эпизоды потери сознания, судорог или нарушения речи?"**
+     *Цель*: Исключить гипертонический криз или цереброваскулярные осложнения.
+   - **"Есть ли наследственная предрасположенность к гипертонии или сердечно-сосудистым заболеваниям?"**
+     *Цель*: Оценить риск развития АГ.
+   - **"Принимаете ли вы какие-либо лекарства (например, оральные контрацептивы, НПВС, кортикостероиды)?"**
+     *Цель*: Выявить возможные причины вторичной гипертензии.
+2. **Рекомендации по дальнейшим действиям**:
+   - **Срочно направить на измерение АД** (если не измерялось ранее) и **консультацию терапевта/кардиолога** для подтверждения диагноза.
+   - **Исключить вторичные причины гипертензии** (например, заболевания почек, эндокринные нарушения) при наличии:
+     - Стойкой АГ у молодых (&lt;30 лет) или пожилых (&gt;60 лет).
+     - Резистентной АГ (АД не снижается на фоне 3 препаратов).
+     - Внезапного ухудшения контроля АГ.
+   - **Объяснить пациенту важность амбулаторного наблюдения**:
+     - АГ часто протекает бессимптомно, но приводит к тяжелым осложнениям (инфаркт, инсульт, ХБП).
+     - Необходимо **вести дневник АД** (измерять 2 раза в день утром и вечером).
+   - **Предупредить о немедленном обращении за медицинской помощью** при:
+     - АД &gt;180/120 мм рт. ст.
+     - Появлении сильных головных болей, тошноты, рвоты, нарушения зрения.
+     - Боли в груди, одышке, онемении конечностей.
+3. **Образовательные материалы для пациента**:
+   - Объяснить, что **головные боли не всегда связаны с АГ**, но требуют обследования.
+   - Подчеркнуть роль **здорового образа жизни**: снижение соли, жиров, регулярная физическая активность, отказ от курения и алкоголя.
+**Важно**: Если у пациента **гипертонический криз** (АД &gt;180/120 мм рт. ст. + симптомы поражения органов-мишеней), **необходимо экстренное направление в стационар**.</t>
+  </si>
+  <si>
+    <t>Не найдено (нестандартный формат)</t>
   </si>
   <si>
     <t>Не применимо (агент без графа не генерирует советы оператору)</t>
@@ -116,17 +148,9 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -142,7 +166,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -150,54 +174,25 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -235,7 +230,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -269,7 +264,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -304,10 +298,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -480,66 +473,63 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="3" width="34.6640625" style="2" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="48" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="128" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
